--- a/configs/lte_channel_config.xlsx
+++ b/configs/lte_channel_config.xlsx
@@ -426,7 +426,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0,300,599</t>
+          <t>是</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
@@ -530,14 +530,18 @@
       <c r="H2" t="n">
         <v>20</v>
       </c>
-      <c r="I2" t="n">
-        <v>300</v>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
       </c>
       <c r="J2" t="n">
         <v>10</v>
       </c>
-      <c r="K2" t="n">
-        <v>100</v>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
       </c>
       <c r="L2" t="n">
         <v>20</v>
@@ -556,7 +560,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1200,1575,1949</t>
+          <t>是</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
@@ -571,14 +575,18 @@
       <c r="H3" t="n">
         <v>20</v>
       </c>
-      <c r="I3" t="n">
-        <v>1575</v>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1575</t>
+        </is>
       </c>
       <c r="J3" t="n">
         <v>20</v>
       </c>
-      <c r="K3" t="n">
-        <v>1300</v>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>1300</t>
+        </is>
       </c>
       <c r="L3" t="n">
         <v>20</v>
@@ -597,7 +605,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2400,2525,2649</t>
+          <t>是</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
@@ -612,14 +620,18 @@
       <c r="H4" t="n">
         <v>10</v>
       </c>
-      <c r="I4" t="n">
-        <v>2525</v>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2525</t>
+        </is>
       </c>
       <c r="J4" t="n">
         <v>10</v>
       </c>
-      <c r="K4" t="n">
-        <v>2450</v>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2450</t>
+        </is>
       </c>
       <c r="L4" t="n">
         <v>10</v>
